--- a/Data/Home/Kitchen.Humidity.xlsx
+++ b/Data/Home/Kitchen.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709370818</v>
+        <v>1712298738</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,10 +502,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: Moist</t>
+          <t>Kitchen.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709443276</v>
+        <v>1712309194</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709461406</v>
+        <v>1712559195</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709752842</v>
+        <v>1712638017</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709788372</v>
+        <v>1713067403</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: Moist</t>
+          <t>Kitchen.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709827362</v>
+        <v>1713075791</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709873047</v>
+        <v>1713169518</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: Moist</t>
+          <t>Kitchen.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710611874</v>
+        <v>1713228685</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1710655155</v>
+        <v>1713264915</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710722574</v>
+        <v>1713359120</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1710819856</v>
+        <v>1713431062</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1710979280</v>
+        <v>1713432105</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1711005763</v>
+        <v>1713441591</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1711546166</v>
+        <v>1713485003</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1711559494</v>
+        <v>1713607532</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +964,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kitchen.Humidity.state: Moist</t>
+          <t>Kitchen.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1711637845</v>
+        <v>1713616762</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,407 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1713630904</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1713680647</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1713702328</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1713713490</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1713722335</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1713756891</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1713778090</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1713786334</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Kitchen.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1713863669</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1713870033</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1713947922</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1714185300</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Kitchen.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
